--- a/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-200_p-10_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-200_p-10_nm_basis-False_nm_modifier-False.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,609 +448,324 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sub6ex1</t>
+          <t>sub1ex1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80.44974437495134</v>
+        <v>78.70223790863243</v>
       </c>
       <c r="C2" t="n">
-        <v>79.982803554588</v>
+        <v>78.55379235462367</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6821611837794384</v>
+        <v>0.6099972868183007</v>
       </c>
       <c r="E2" t="n">
-        <v>80.44974437495134</v>
+        <v>78.70223790863243</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sub6ex2</t>
+          <t>sub1ex2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84.575731623976</v>
+        <v>76.5238453619841</v>
       </c>
       <c r="C3" t="n">
-        <v>83.94758897697733</v>
+        <v>76.57469774350915</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4700516133879621</v>
+        <v>0.6176566949735085</v>
       </c>
       <c r="E3" t="n">
-        <v>84.57573162397598</v>
+        <v>76.5238453619841</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sub6ex3</t>
+          <t>sub1ex3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84.10479329405965</v>
+        <v>71.68747134490783</v>
       </c>
       <c r="C4" t="n">
-        <v>83.43035278727514</v>
+        <v>71.50291195066862</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4421738617160978</v>
+        <v>0.6872832434872787</v>
       </c>
       <c r="E4" t="n">
-        <v>84.10479329405965</v>
+        <v>71.68747134490783</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sub7ex1</t>
+          <t>sub2ex1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.97397036306543</v>
+        <v>78.12610835733872</v>
       </c>
       <c r="C5" t="n">
-        <v>80.9112368413752</v>
+        <v>78.07225208458954</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4643361548272272</v>
+        <v>0.5978290871717036</v>
       </c>
       <c r="E5" t="n">
-        <v>80.97397036306543</v>
+        <v>78.12610835733872</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sub7ex2</t>
+          <t>sub2ex2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80.56618136835094</v>
+        <v>77.07160096540628</v>
       </c>
       <c r="C6" t="n">
-        <v>80.57657152893762</v>
+        <v>76.2571405237172</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5077931510905425</v>
+        <v>0.6881659299057599</v>
       </c>
       <c r="E6" t="n">
-        <v>80.56618136835094</v>
+        <v>77.07160096540628</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sub7ex3</t>
+          <t>sub2ex3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>75.34649953719322</v>
+        <v>80.2958503101238</v>
       </c>
       <c r="C7" t="n">
-        <v>75.19548507216255</v>
+        <v>80.19786009977911</v>
       </c>
       <c r="D7" t="n">
-        <v>0.650793656334281</v>
+        <v>0.4631219813600183</v>
       </c>
       <c r="E7" t="n">
-        <v>75.34649953719322</v>
+        <v>80.29585031012378</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sub8ex1</t>
+          <t>sub3ex1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84.5821330634348</v>
+        <v>70.74749781572504</v>
       </c>
       <c r="C8" t="n">
-        <v>84.34023807948125</v>
+        <v>70.72552158609751</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3947218521730974</v>
+        <v>0.7388943895697594</v>
       </c>
       <c r="E8" t="n">
-        <v>84.5821330634348</v>
+        <v>70.74749781572504</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sub8ex2</t>
+          <t>sub3ex2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.96891841624928</v>
+        <v>76.09849566172718</v>
       </c>
       <c r="C9" t="n">
-        <v>86.90748050142808</v>
+        <v>74.64472690871801</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3168373483388374</v>
+        <v>0.690858487947844</v>
       </c>
       <c r="E9" t="n">
-        <v>86.96891841624928</v>
+        <v>76.09849566172718</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sub8ex3</t>
+          <t>sub3ex3</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91.26912862568015</v>
+        <v>84.1951919999308</v>
       </c>
       <c r="C10" t="n">
-        <v>91.28644691554794</v>
+        <v>83.85626911504779</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2260707137601761</v>
+        <v>0.4189860889688134</v>
       </c>
       <c r="E10" t="n">
-        <v>91.26912862568015</v>
+        <v>84.1951919999308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sub9ex1</t>
+          <t>sub4ex1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88.70292995614149</v>
+        <v>78.76313808942984</v>
       </c>
       <c r="C11" t="n">
-        <v>88.66354852748093</v>
+        <v>78.25655384533744</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3270958530192729</v>
+        <v>0.7134155191791555</v>
       </c>
       <c r="E11" t="n">
-        <v>88.70292995614149</v>
+        <v>78.76313808942984</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sub9ex2</t>
+          <t>sub4ex2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80.59066254898399</v>
+        <v>66.08378965215962</v>
       </c>
       <c r="C12" t="n">
-        <v>79.95041519199138</v>
+        <v>66.09701597530686</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5534041484507422</v>
+        <v>0.8788097468515238</v>
       </c>
       <c r="E12" t="n">
-        <v>80.59066254898399</v>
+        <v>66.08378965215962</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sub9ex3</t>
+          <t>sub4ex3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>88.7069092293186</v>
+        <v>73.68013564131176</v>
       </c>
       <c r="C13" t="n">
-        <v>88.10698301250414</v>
+        <v>73.2889199833068</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3839442447332355</v>
+        <v>0.7188776424775521</v>
       </c>
       <c r="E13" t="n">
-        <v>88.7069092293186</v>
+        <v>73.68013564131178</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sub10ex1</t>
+          <t>sub5ex1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>74.69156307580515</v>
+        <v>74.32235572972084</v>
       </c>
       <c r="C14" t="n">
-        <v>74.15353350862162</v>
+        <v>73.94552857080694</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6563034517069657</v>
+        <v>0.705831055343151</v>
       </c>
       <c r="E14" t="n">
-        <v>74.69156307580515</v>
+        <v>74.32235572972084</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sub10ex2</t>
+          <t>sub5ex2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>77.47108539001202</v>
+        <v>76.54953762575801</v>
       </c>
       <c r="C15" t="n">
-        <v>77.32138679943948</v>
+        <v>75.60082534287619</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6103073492646217</v>
+        <v>0.6605028440710157</v>
       </c>
       <c r="E15" t="n">
-        <v>77.47108539001202</v>
+        <v>76.54953762575801</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sub10ex3</t>
+          <t>sub5ex3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>75.0341265927906</v>
+        <v>70.83011098711927</v>
       </c>
       <c r="C16" t="n">
-        <v>75.26072733205055</v>
+        <v>71.02386605050312</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6864370019485553</v>
+        <v>0.7877616467264792</v>
       </c>
       <c r="E16" t="n">
-        <v>75.03412659279059</v>
+        <v>70.83011098711927</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sub11ex1</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.60262632029689</v>
+        <v>75.57849116341838</v>
       </c>
       <c r="C17" t="n">
-        <v>83.36168572234885</v>
+        <v>75.23985880899252</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4668867199216038</v>
+        <v>0.6651994429901241</v>
       </c>
       <c r="E17" t="n">
-        <v>83.60262632029689</v>
+        <v>75.57849116341838</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sub11ex2</t>
+          <t>Std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>79.4344241732195</v>
+        <v>4.348058371819933</v>
       </c>
       <c r="C18" t="n">
-        <v>78.696939769406</v>
+        <v>4.253799328241276</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6216972189179312</v>
+        <v>0.1113364684932138</v>
       </c>
       <c r="E18" t="n">
-        <v>79.4344241732195</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sub11ex3</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>88.20474225555584</v>
-      </c>
-      <c r="C19" t="n">
-        <v>88.20193694534417</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3476892431577047</v>
-      </c>
-      <c r="E19" t="n">
-        <v>88.20474225555584</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>sub12ex1</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>79.62222856599105</v>
-      </c>
-      <c r="C20" t="n">
-        <v>78.83666616476224</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.5469612072532375</v>
-      </c>
-      <c r="E20" t="n">
-        <v>79.62222856599105</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>sub12ex2</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>72.60054152717585</v>
-      </c>
-      <c r="C21" t="n">
-        <v>71.89452039812004</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.7095986675626288</v>
-      </c>
-      <c r="E21" t="n">
-        <v>72.60054152717585</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sub12ex3</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>79.81790499917818</v>
-      </c>
-      <c r="C22" t="n">
-        <v>79.70003282038935</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.5507639246992767</v>
-      </c>
-      <c r="E22" t="n">
-        <v>79.8179049991782</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>sub13ex1</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>78.01330461336171</v>
-      </c>
-      <c r="C23" t="n">
-        <v>77.8342326693396</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.6280005905777216</v>
-      </c>
-      <c r="E23" t="n">
-        <v>78.01330461336171</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sub13ex2</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>82.8915475047362</v>
-      </c>
-      <c r="C24" t="n">
-        <v>82.69971416824079</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.4654913346671189</v>
-      </c>
-      <c r="E24" t="n">
-        <v>82.8915475047362</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>sub13ex3</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>83.95730066869091</v>
-      </c>
-      <c r="C25" t="n">
-        <v>83.65056303596756</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.4488191062584519</v>
-      </c>
-      <c r="E25" t="n">
-        <v>83.95730066869091</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>sub14ex1</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>81.25139490826045</v>
-      </c>
-      <c r="C26" t="n">
-        <v>81.03611411813272</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.5015344141361614</v>
-      </c>
-      <c r="E26" t="n">
-        <v>81.25139490826045</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>sub14ex2</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>71.09836590281922</v>
-      </c>
-      <c r="C27" t="n">
-        <v>70.89905131463067</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.7661911045822005</v>
-      </c>
-      <c r="E27" t="n">
-        <v>71.09836590281922</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>sub14ex3</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>79.00327857507418</v>
-      </c>
-      <c r="C28" t="n">
-        <v>78.36948044307701</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.6351455733180046</v>
-      </c>
-      <c r="E28" t="n">
-        <v>79.00327857507418</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>sub15ex1</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>88.43986539675949</v>
-      </c>
-      <c r="C29" t="n">
-        <v>88.47357294576622</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.3670114732114598</v>
-      </c>
-      <c r="E29" t="n">
-        <v>88.43986539675949</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>sub15ex2</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>91.39075597539771</v>
-      </c>
-      <c r="C30" t="n">
-        <v>91.29764815450143</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.2683612560465311</v>
-      </c>
-      <c r="E30" t="n">
-        <v>91.39075597539771</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sub15ex3</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>90.56583534459641</v>
-      </c>
-      <c r="C31" t="n">
-        <v>89.98011888277564</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.2680967580759898</v>
-      </c>
-      <c r="E31" t="n">
-        <v>90.56583534459641</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>82.13094980637086</v>
-      </c>
-      <c r="C32" t="n">
-        <v>81.83223587275545</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.4988226725639024</v>
-      </c>
-      <c r="E32" t="n">
-        <v>82.13094980637086</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Std</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5.447640057539839</v>
-      </c>
-      <c r="C33" t="n">
-        <v>5.500720649932581</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.1438698730670233</v>
-      </c>
-      <c r="E33" t="n">
-        <v>5.447640057539839</v>
+        <v>4.348058371819932</v>
       </c>
     </row>
   </sheetData>
@@ -1096,16 +811,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.13094980637086</v>
+        <v>75.57849116341838</v>
       </c>
       <c r="B2" t="n">
-        <v>81.83223587275545</v>
+        <v>75.23985880899252</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4988226725639024</v>
+        <v>0.6651994429901241</v>
       </c>
       <c r="D2" t="n">
-        <v>82.13094980637086</v>
+        <v>75.57849116341838</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1115,16 +830,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5.447640057539839</v>
+        <v>4.348058371819933</v>
       </c>
       <c r="B3" t="n">
-        <v>5.500720649932581</v>
+        <v>4.253799328241276</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1438698730670233</v>
+        <v>0.1113364684932138</v>
       </c>
       <c r="D3" t="n">
-        <v>5.447640057539839</v>
+        <v>4.348058371819932</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1190,28 +905,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.13094980637086</v>
+        <v>75.57849116341838</v>
       </c>
       <c r="B2" t="n">
-        <v>5.447640057539839</v>
+        <v>4.348058371819933</v>
       </c>
       <c r="C2" t="n">
-        <v>81.83223587275545</v>
+        <v>75.23985880899252</v>
       </c>
       <c r="D2" t="n">
-        <v>5.500720649932581</v>
+        <v>4.253799328241276</v>
       </c>
       <c r="E2" t="n">
-        <v>82.13094980637086</v>
+        <v>75.57849116341838</v>
       </c>
       <c r="F2" t="n">
-        <v>5.447640057539839</v>
+        <v>4.348058371819932</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4988226725639024</v>
+        <v>0.6651994429901241</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1438698730670233</v>
+        <v>0.1113364684932138</v>
       </c>
     </row>
   </sheetData>
